--- a/PyFCS/test/benchmark_comparation.xlsx
+++ b/PyFCS/test/benchmark_comparation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafav\Desktop\Tesis_Code\PyFCS_GUI\PyFCS\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11555E81-5959-4260-B6F1-4735E45D749F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33552F8-58B2-4855-8C67-F6310304C3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
   <si>
     <t>Metrics</t>
   </si>
@@ -52,6 +52,15 @@
   </si>
   <si>
     <t>n = 50 colors</t>
+  </si>
+  <si>
+    <t>ISCC_NBS_COMPLETE N=267 colors</t>
+  </si>
+  <si>
+    <t>ISCC_NBS_EXTENDED N=20 colors</t>
+  </si>
+  <si>
+    <t>ISCC_NBS_BASIC N=13 colors</t>
   </si>
 </sst>
 </file>
@@ -87,9 +96,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -372,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.36328125" customWidth="1"/>
@@ -479,7 +491,142 @@
         <v>5046.74</v>
       </c>
     </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.80781499999999995</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1.482</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1">
+        <v>500.69</v>
+      </c>
+      <c r="D11" s="2">
+        <v>801.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1184.1099999999999</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1450.48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C13" s="1"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1.228667</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2.0550000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1">
+        <v>572.29999999999995</v>
+      </c>
+      <c r="D15" s="2">
+        <v>905.68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1732.61</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2264.2600000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C17" s="1"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>62.69126</v>
+      </c>
+      <c r="D18" s="2">
+        <v>109.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2144.09</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3030.54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="1">
+        <v>26279.54</v>
+      </c>
+      <c r="D20" s="2">
+        <v>34993.730000000003</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>